--- a/SH1000 intensities.xlsx
+++ b/SH1000 intensities.xlsx
@@ -7,12 +7,12 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SH1000 Ebba680+ R3 airyscan" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SH1000 Ebba680+ R2 airyscan" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SH1000 Ebba680- R3 airyscan" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SH1000 Ebba680- R2 airyscan" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SH1000 Ebba680- R1 airyscan" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SH1000 Ebba680+ R1 airyscan" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SH1000 Ebba680+ R1 airy" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SH1000 Ebba680+ R2 airy" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SH1000 Ebba680+ R3 airy" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SH1000 Ebba680- R1 airy" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SH1000 Ebba680- R2 airy" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SH1000 Ebba680- R3 airy" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -450,10 +450,10 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8000959</v>
+        <v>26324630</v>
       </c>
       <c r="C2" t="n">
-        <v>1843043</v>
+        <v>4250934</v>
       </c>
     </row>
     <row r="3">
@@ -461,10 +461,10 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>8129208</v>
+        <v>26955106</v>
       </c>
       <c r="C3" t="n">
-        <v>1881535</v>
+        <v>4137408</v>
       </c>
     </row>
     <row r="4">
@@ -472,10 +472,10 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>8427625</v>
+        <v>29518833</v>
       </c>
       <c r="C4" t="n">
-        <v>1930100</v>
+        <v>4289014</v>
       </c>
     </row>
     <row r="5">
@@ -483,10 +483,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>8776570</v>
+        <v>33614939</v>
       </c>
       <c r="C5" t="n">
-        <v>2027491</v>
+        <v>4504180</v>
       </c>
     </row>
     <row r="6">
@@ -494,10 +494,10 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>9209281</v>
+        <v>39197268</v>
       </c>
       <c r="C6" t="n">
-        <v>2098933</v>
+        <v>4881833</v>
       </c>
     </row>
     <row r="7">
@@ -505,10 +505,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9478631</v>
+        <v>47276917</v>
       </c>
       <c r="C7" t="n">
-        <v>2182463</v>
+        <v>5361454</v>
       </c>
     </row>
     <row r="8">
@@ -516,10 +516,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9775144</v>
+        <v>61962814</v>
       </c>
       <c r="C8" t="n">
-        <v>2242409</v>
+        <v>6115230</v>
       </c>
     </row>
     <row r="9">
@@ -527,10 +527,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10020559</v>
+        <v>78178217</v>
       </c>
       <c r="C9" t="n">
-        <v>2315614</v>
+        <v>6906508</v>
       </c>
     </row>
     <row r="10">
@@ -538,10 +538,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>10206994</v>
+        <v>97304114</v>
       </c>
       <c r="C10" t="n">
-        <v>2383799</v>
+        <v>7783612</v>
       </c>
     </row>
     <row r="11">
@@ -549,10 +549,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>10699302</v>
+        <v>115683400</v>
       </c>
       <c r="C11" t="n">
-        <v>2460490</v>
+        <v>8983556</v>
       </c>
     </row>
     <row r="12">
@@ -560,10 +560,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>11202133</v>
+        <v>139717455</v>
       </c>
       <c r="C12" t="n">
-        <v>2536298</v>
+        <v>10938323</v>
       </c>
     </row>
     <row r="13">
@@ -571,10 +571,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11561904</v>
+        <v>156163150</v>
       </c>
       <c r="C13" t="n">
-        <v>2631273</v>
+        <v>13554212</v>
       </c>
     </row>
     <row r="14">
@@ -582,10 +582,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>12236809</v>
+        <v>165111178</v>
       </c>
       <c r="C14" t="n">
-        <v>2780816</v>
+        <v>18268830</v>
       </c>
     </row>
     <row r="15">
@@ -593,10 +593,10 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>13308962</v>
+        <v>170285190</v>
       </c>
       <c r="C15" t="n">
-        <v>2960395</v>
+        <v>24455011</v>
       </c>
     </row>
     <row r="16">
@@ -604,10 +604,10 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>14222059</v>
+        <v>169453790</v>
       </c>
       <c r="C16" t="n">
-        <v>3147793</v>
+        <v>31226957</v>
       </c>
     </row>
     <row r="17">
@@ -615,10 +615,10 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>15234814</v>
+        <v>163622278</v>
       </c>
       <c r="C17" t="n">
-        <v>3350374</v>
+        <v>35497646</v>
       </c>
     </row>
     <row r="18">
@@ -626,10 +626,10 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>16087549</v>
+        <v>159434144</v>
       </c>
       <c r="C18" t="n">
-        <v>3493806</v>
+        <v>38206123</v>
       </c>
     </row>
     <row r="19">
@@ -637,10 +637,10 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>17327159</v>
+        <v>155444368</v>
       </c>
       <c r="C19" t="n">
-        <v>3675987</v>
+        <v>39638819</v>
       </c>
     </row>
     <row r="20">
@@ -648,10 +648,10 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>18811488</v>
+        <v>153517152</v>
       </c>
       <c r="C20" t="n">
-        <v>3939850</v>
+        <v>40431920</v>
       </c>
     </row>
     <row r="21">
@@ -659,10 +659,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>20914838</v>
+        <v>151347820</v>
       </c>
       <c r="C21" t="n">
-        <v>4302127</v>
+        <v>40851996</v>
       </c>
     </row>
     <row r="22">
@@ -670,10 +670,10 @@
         <v>20</v>
       </c>
       <c r="B22" t="n">
-        <v>23412366</v>
+        <v>148698569</v>
       </c>
       <c r="C22" t="n">
-        <v>4704785</v>
+        <v>40935814</v>
       </c>
     </row>
     <row r="23">
@@ -681,10 +681,10 @@
         <v>21</v>
       </c>
       <c r="B23" t="n">
-        <v>27829377</v>
+        <v>146698186</v>
       </c>
       <c r="C23" t="n">
-        <v>5334987</v>
+        <v>41089966</v>
       </c>
     </row>
     <row r="24">
@@ -692,10 +692,10 @@
         <v>22</v>
       </c>
       <c r="B24" t="n">
-        <v>33195261</v>
+        <v>145040770</v>
       </c>
       <c r="C24" t="n">
-        <v>5999124</v>
+        <v>41351905</v>
       </c>
     </row>
     <row r="25">
@@ -703,10 +703,10 @@
         <v>23</v>
       </c>
       <c r="B25" t="n">
-        <v>39228849</v>
+        <v>143152876</v>
       </c>
       <c r="C25" t="n">
-        <v>6743940</v>
+        <v>41605274</v>
       </c>
     </row>
     <row r="26">
@@ -714,10 +714,10 @@
         <v>24</v>
       </c>
       <c r="B26" t="n">
-        <v>45509179</v>
+        <v>142142240</v>
       </c>
       <c r="C26" t="n">
-        <v>7394543</v>
+        <v>41755659</v>
       </c>
     </row>
     <row r="27">
@@ -725,10 +725,10 @@
         <v>25</v>
       </c>
       <c r="B27" t="n">
-        <v>51265637</v>
+        <v>141170734</v>
       </c>
       <c r="C27" t="n">
-        <v>8120995</v>
+        <v>41826962</v>
       </c>
     </row>
     <row r="28">
@@ -736,10 +736,10 @@
         <v>26</v>
       </c>
       <c r="B28" t="n">
-        <v>61202343</v>
+        <v>140414331</v>
       </c>
       <c r="C28" t="n">
-        <v>9241427</v>
+        <v>41763064</v>
       </c>
     </row>
     <row r="29">
@@ -747,10 +747,10 @@
         <v>27</v>
       </c>
       <c r="B29" t="n">
-        <v>73316362</v>
+        <v>138948228</v>
       </c>
       <c r="C29" t="n">
-        <v>10662746</v>
+        <v>41641668</v>
       </c>
     </row>
     <row r="30">
@@ -758,10 +758,10 @@
         <v>28</v>
       </c>
       <c r="B30" t="n">
-        <v>88810859</v>
+        <v>137810916</v>
       </c>
       <c r="C30" t="n">
-        <v>13641899</v>
+        <v>41401513</v>
       </c>
     </row>
     <row r="31">
@@ -769,10 +769,10 @@
         <v>29</v>
       </c>
       <c r="B31" t="n">
-        <v>103141215</v>
+        <v>136084911</v>
       </c>
       <c r="C31" t="n">
-        <v>18111034</v>
+        <v>41212197</v>
       </c>
     </row>
     <row r="32">
@@ -780,10 +780,10 @@
         <v>30</v>
       </c>
       <c r="B32" t="n">
-        <v>113035399</v>
+        <v>134694338</v>
       </c>
       <c r="C32" t="n">
-        <v>24818744</v>
+        <v>40800403</v>
       </c>
     </row>
     <row r="33">
@@ -791,10 +791,10 @@
         <v>31</v>
       </c>
       <c r="B33" t="n">
-        <v>119654409</v>
+        <v>133134189</v>
       </c>
       <c r="C33" t="n">
-        <v>30933689</v>
+        <v>40363859</v>
       </c>
     </row>
     <row r="34">
@@ -802,10 +802,10 @@
         <v>32</v>
       </c>
       <c r="B34" t="n">
-        <v>122267098</v>
+        <v>132883917</v>
       </c>
       <c r="C34" t="n">
-        <v>35455218</v>
+        <v>39913159</v>
       </c>
     </row>
     <row r="35">
@@ -813,10 +813,10 @@
         <v>33</v>
       </c>
       <c r="B35" t="n">
-        <v>122303204</v>
+        <v>132048166</v>
       </c>
       <c r="C35" t="n">
-        <v>38503348</v>
+        <v>39552114</v>
       </c>
     </row>
     <row r="36">
@@ -824,10 +824,10 @@
         <v>34</v>
       </c>
       <c r="B36" t="n">
-        <v>121426515</v>
+        <v>131558070</v>
       </c>
       <c r="C36" t="n">
-        <v>40124253</v>
+        <v>39193328</v>
       </c>
     </row>
     <row r="37">
@@ -835,10 +835,10 @@
         <v>35</v>
       </c>
       <c r="B37" t="n">
-        <v>120033875</v>
+        <v>131035166</v>
       </c>
       <c r="C37" t="n">
-        <v>41026950</v>
+        <v>38781882</v>
       </c>
     </row>
     <row r="38">
@@ -846,10 +846,10 @@
         <v>36</v>
       </c>
       <c r="B38" t="n">
-        <v>119071971</v>
+        <v>130536124</v>
       </c>
       <c r="C38" t="n">
-        <v>41455542</v>
+        <v>38258189</v>
       </c>
     </row>
     <row r="39">
@@ -857,10 +857,10 @@
         <v>37</v>
       </c>
       <c r="B39" t="n">
-        <v>117803683</v>
+        <v>129985449</v>
       </c>
       <c r="C39" t="n">
-        <v>41963118</v>
+        <v>37831845</v>
       </c>
     </row>
     <row r="40">
@@ -868,10 +868,10 @@
         <v>38</v>
       </c>
       <c r="B40" t="n">
-        <v>117002092</v>
+        <v>129570538</v>
       </c>
       <c r="C40" t="n">
-        <v>42408254</v>
+        <v>37286752</v>
       </c>
     </row>
     <row r="41">
@@ -879,10 +879,10 @@
         <v>39</v>
       </c>
       <c r="B41" t="n">
-        <v>116509078</v>
+        <v>129228109</v>
       </c>
       <c r="C41" t="n">
-        <v>42510403</v>
+        <v>36658458</v>
       </c>
     </row>
     <row r="42">
@@ -890,10 +890,10 @@
         <v>40</v>
       </c>
       <c r="B42" t="n">
-        <v>115941184</v>
+        <v>128461563</v>
       </c>
       <c r="C42" t="n">
-        <v>42558275</v>
+        <v>36240308</v>
       </c>
     </row>
     <row r="43">
@@ -901,10 +901,10 @@
         <v>41</v>
       </c>
       <c r="B43" t="n">
-        <v>115720623</v>
+        <v>128062688</v>
       </c>
       <c r="C43" t="n">
-        <v>42572114</v>
+        <v>35762401</v>
       </c>
     </row>
     <row r="44">
@@ -912,10 +912,10 @@
         <v>42</v>
       </c>
       <c r="B44" t="n">
-        <v>115608917</v>
+        <v>126957643</v>
       </c>
       <c r="C44" t="n">
-        <v>42424511</v>
+        <v>35476404</v>
       </c>
     </row>
     <row r="45">
@@ -923,10 +923,10 @@
         <v>43</v>
       </c>
       <c r="B45" t="n">
-        <v>115720712</v>
+        <v>126518864</v>
       </c>
       <c r="C45" t="n">
-        <v>42366048</v>
+        <v>35132771</v>
       </c>
     </row>
     <row r="46">
@@ -934,10 +934,10 @@
         <v>44</v>
       </c>
       <c r="B46" t="n">
-        <v>115175611</v>
+        <v>125008559</v>
       </c>
       <c r="C46" t="n">
-        <v>42302353</v>
+        <v>34714378</v>
       </c>
     </row>
     <row r="47">
@@ -945,10 +945,10 @@
         <v>45</v>
       </c>
       <c r="B47" t="n">
-        <v>114764593</v>
+        <v>123665083</v>
       </c>
       <c r="C47" t="n">
-        <v>42185607</v>
+        <v>34178507</v>
       </c>
     </row>
     <row r="48">
@@ -956,10 +956,10 @@
         <v>46</v>
       </c>
       <c r="B48" t="n">
-        <v>114486114</v>
+        <v>122432970</v>
       </c>
       <c r="C48" t="n">
-        <v>41890879</v>
+        <v>33804431</v>
       </c>
     </row>
     <row r="49">
@@ -967,10 +967,10 @@
         <v>47</v>
       </c>
       <c r="B49" t="n">
-        <v>113724144</v>
+        <v>120570392</v>
       </c>
       <c r="C49" t="n">
-        <v>41486415</v>
+        <v>33376564</v>
       </c>
     </row>
     <row r="50">
@@ -978,10 +978,10 @@
         <v>48</v>
       </c>
       <c r="B50" t="n">
-        <v>112877629</v>
+        <v>119782046</v>
       </c>
       <c r="C50" t="n">
-        <v>41030798</v>
+        <v>32984712</v>
       </c>
     </row>
     <row r="51">
@@ -989,10 +989,10 @@
         <v>49</v>
       </c>
       <c r="B51" t="n">
-        <v>112643249</v>
+        <v>119189572</v>
       </c>
       <c r="C51" t="n">
-        <v>40619314</v>
+        <v>32777728</v>
       </c>
     </row>
     <row r="52">
@@ -1000,10 +1000,10 @@
         <v>50</v>
       </c>
       <c r="B52" t="n">
-        <v>112188396</v>
+        <v>118369268</v>
       </c>
       <c r="C52" t="n">
-        <v>40211420</v>
+        <v>32458979</v>
       </c>
     </row>
     <row r="53">
@@ -1011,10 +1011,10 @@
         <v>51</v>
       </c>
       <c r="B53" t="n">
-        <v>111247988</v>
+        <v>117914753</v>
       </c>
       <c r="C53" t="n">
-        <v>39634669</v>
+        <v>32179500</v>
       </c>
     </row>
     <row r="54">
@@ -1022,10 +1022,10 @@
         <v>52</v>
       </c>
       <c r="B54" t="n">
-        <v>110749602</v>
+        <v>117519054</v>
       </c>
       <c r="C54" t="n">
-        <v>39139787</v>
+        <v>31802545</v>
       </c>
     </row>
     <row r="55">
@@ -1033,10 +1033,10 @@
         <v>53</v>
       </c>
       <c r="B55" t="n">
-        <v>109372333</v>
+        <v>116666397</v>
       </c>
       <c r="C55" t="n">
-        <v>38411710</v>
+        <v>31499987</v>
       </c>
     </row>
   </sheetData>
@@ -1070,10 +1070,10 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5533902</v>
+        <v>10107240</v>
       </c>
       <c r="C2" t="n">
-        <v>1708577</v>
+        <v>3561584</v>
       </c>
     </row>
     <row r="3">
@@ -1081,10 +1081,10 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5586524</v>
+        <v>10255492</v>
       </c>
       <c r="C3" t="n">
-        <v>1721302</v>
+        <v>3480817</v>
       </c>
     </row>
     <row r="4">
@@ -1092,10 +1092,10 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>5740294</v>
+        <v>10693804</v>
       </c>
       <c r="C4" t="n">
-        <v>1745922</v>
+        <v>3484012</v>
       </c>
     </row>
     <row r="5">
@@ -1103,10 +1103,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>5907804</v>
+        <v>11048884</v>
       </c>
       <c r="C5" t="n">
-        <v>1783015</v>
+        <v>3516320</v>
       </c>
     </row>
     <row r="6">
@@ -1114,10 +1114,10 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>6115861</v>
+        <v>11216329</v>
       </c>
       <c r="C6" t="n">
-        <v>1841625</v>
+        <v>3560786</v>
       </c>
     </row>
     <row r="7">
@@ -1125,10 +1125,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>6338140</v>
+        <v>11619644</v>
       </c>
       <c r="C7" t="n">
-        <v>1884544</v>
+        <v>3646680</v>
       </c>
     </row>
     <row r="8">
@@ -1136,10 +1136,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>6494190</v>
+        <v>12144061</v>
       </c>
       <c r="C8" t="n">
-        <v>1927289</v>
+        <v>3779289</v>
       </c>
     </row>
     <row r="9">
@@ -1147,10 +1147,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6815690</v>
+        <v>12975842</v>
       </c>
       <c r="C9" t="n">
-        <v>1983371</v>
+        <v>3926371</v>
       </c>
     </row>
     <row r="10">
@@ -1158,10 +1158,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6938167</v>
+        <v>13743895</v>
       </c>
       <c r="C10" t="n">
-        <v>2012183</v>
+        <v>4188057</v>
       </c>
     </row>
     <row r="11">
@@ -1169,10 +1169,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>6979939</v>
+        <v>14657313</v>
       </c>
       <c r="C11" t="n">
-        <v>2057838</v>
+        <v>4389381</v>
       </c>
     </row>
     <row r="12">
@@ -1180,10 +1180,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>7261449</v>
+        <v>15786364</v>
       </c>
       <c r="C12" t="n">
-        <v>2082977</v>
+        <v>4624450</v>
       </c>
     </row>
     <row r="13">
@@ -1191,10 +1191,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>7474942</v>
+        <v>16867864</v>
       </c>
       <c r="C13" t="n">
-        <v>2156682</v>
+        <v>4874080</v>
       </c>
     </row>
     <row r="14">
@@ -1202,10 +1202,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>7836064</v>
+        <v>17846287</v>
       </c>
       <c r="C14" t="n">
-        <v>2223300</v>
+        <v>5104918</v>
       </c>
     </row>
     <row r="15">
@@ -1213,10 +1213,10 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>8158115</v>
+        <v>19258265</v>
       </c>
       <c r="C15" t="n">
-        <v>2302606</v>
+        <v>5411595</v>
       </c>
     </row>
     <row r="16">
@@ -1224,10 +1224,10 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>8674555</v>
+        <v>21006358</v>
       </c>
       <c r="C16" t="n">
-        <v>2419886</v>
+        <v>5811084</v>
       </c>
     </row>
     <row r="17">
@@ -1235,10 +1235,10 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>9032233</v>
+        <v>23769749</v>
       </c>
       <c r="C17" t="n">
-        <v>2526879</v>
+        <v>6343921</v>
       </c>
     </row>
     <row r="18">
@@ -1246,10 +1246,10 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>9439963</v>
+        <v>27472785</v>
       </c>
       <c r="C18" t="n">
-        <v>2603939</v>
+        <v>7035511</v>
       </c>
     </row>
     <row r="19">
@@ -1257,10 +1257,10 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>10001097</v>
+        <v>31772420</v>
       </c>
       <c r="C19" t="n">
-        <v>2709927</v>
+        <v>7769656</v>
       </c>
     </row>
     <row r="20">
@@ -1268,10 +1268,10 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>10445083</v>
+        <v>37064761</v>
       </c>
       <c r="C20" t="n">
-        <v>2804235</v>
+        <v>8574642</v>
       </c>
     </row>
     <row r="21">
@@ -1279,10 +1279,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>11148473</v>
+        <v>41686846</v>
       </c>
       <c r="C21" t="n">
-        <v>2972572</v>
+        <v>9240109</v>
       </c>
     </row>
     <row r="22">
@@ -1290,10 +1290,10 @@
         <v>20</v>
       </c>
       <c r="B22" t="n">
-        <v>12147543</v>
+        <v>47359815</v>
       </c>
       <c r="C22" t="n">
-        <v>3149654</v>
+        <v>10024403</v>
       </c>
     </row>
     <row r="23">
@@ -1301,10 +1301,10 @@
         <v>21</v>
       </c>
       <c r="B23" t="n">
-        <v>13315545</v>
+        <v>54377577</v>
       </c>
       <c r="C23" t="n">
-        <v>3383044</v>
+        <v>10836582</v>
       </c>
     </row>
     <row r="24">
@@ -1312,10 +1312,10 @@
         <v>22</v>
       </c>
       <c r="B24" t="n">
-        <v>14700604</v>
+        <v>63436807</v>
       </c>
       <c r="C24" t="n">
-        <v>3610936</v>
+        <v>12164034</v>
       </c>
     </row>
     <row r="25">
@@ -1323,10 +1323,10 @@
         <v>23</v>
       </c>
       <c r="B25" t="n">
-        <v>15921505</v>
+        <v>80371228</v>
       </c>
       <c r="C25" t="n">
-        <v>3847428</v>
+        <v>14794497</v>
       </c>
     </row>
     <row r="26">
@@ -1334,10 +1334,10 @@
         <v>24</v>
       </c>
       <c r="B26" t="n">
-        <v>17031548</v>
+        <v>101961167</v>
       </c>
       <c r="C26" t="n">
-        <v>4054476</v>
+        <v>18873997</v>
       </c>
     </row>
     <row r="27">
@@ -1345,10 +1345,10 @@
         <v>25</v>
       </c>
       <c r="B27" t="n">
-        <v>18225583</v>
+        <v>122247537</v>
       </c>
       <c r="C27" t="n">
-        <v>4251884</v>
+        <v>25523184</v>
       </c>
     </row>
     <row r="28">
@@ -1356,10 +1356,10 @@
         <v>26</v>
       </c>
       <c r="B28" t="n">
-        <v>19829265</v>
+        <v>134040325</v>
       </c>
       <c r="C28" t="n">
-        <v>4492861</v>
+        <v>33982738</v>
       </c>
     </row>
     <row r="29">
@@ -1367,10 +1367,10 @@
         <v>27</v>
       </c>
       <c r="B29" t="n">
-        <v>21610154</v>
+        <v>141080528</v>
       </c>
       <c r="C29" t="n">
-        <v>4743174</v>
+        <v>42280642</v>
       </c>
     </row>
     <row r="30">
@@ -1378,10 +1378,10 @@
         <v>28</v>
       </c>
       <c r="B30" t="n">
-        <v>24092527</v>
+        <v>145483362</v>
       </c>
       <c r="C30" t="n">
-        <v>5133499</v>
+        <v>49233128</v>
       </c>
     </row>
     <row r="31">
@@ -1389,10 +1389,10 @@
         <v>29</v>
       </c>
       <c r="B31" t="n">
-        <v>28079728</v>
+        <v>146388034</v>
       </c>
       <c r="C31" t="n">
-        <v>5629281</v>
+        <v>55283044</v>
       </c>
     </row>
     <row r="32">
@@ -1400,10 +1400,10 @@
         <v>30</v>
       </c>
       <c r="B32" t="n">
-        <v>34112114</v>
+        <v>144518805</v>
       </c>
       <c r="C32" t="n">
-        <v>6378816</v>
+        <v>61323620</v>
       </c>
     </row>
     <row r="33">
@@ -1411,10 +1411,10 @@
         <v>31</v>
       </c>
       <c r="B33" t="n">
-        <v>42734395</v>
+        <v>140989620</v>
       </c>
       <c r="C33" t="n">
-        <v>7455889</v>
+        <v>64253083</v>
       </c>
     </row>
     <row r="34">
@@ -1422,10 +1422,10 @@
         <v>32</v>
       </c>
       <c r="B34" t="n">
-        <v>55699250</v>
+        <v>137883323</v>
       </c>
       <c r="C34" t="n">
-        <v>8646688</v>
+        <v>65262146</v>
       </c>
     </row>
     <row r="35">
@@ -1433,10 +1433,10 @@
         <v>33</v>
       </c>
       <c r="B35" t="n">
-        <v>67877463</v>
+        <v>135721808</v>
       </c>
       <c r="C35" t="n">
-        <v>9934244</v>
+        <v>65670396</v>
       </c>
     </row>
     <row r="36">
@@ -1444,10 +1444,10 @@
         <v>34</v>
       </c>
       <c r="B36" t="n">
-        <v>87661197</v>
+        <v>134371738</v>
       </c>
       <c r="C36" t="n">
-        <v>12162810</v>
+        <v>65984578</v>
       </c>
     </row>
     <row r="37">
@@ -1455,10 +1455,10 @@
         <v>35</v>
       </c>
       <c r="B37" t="n">
-        <v>104548007</v>
+        <v>133498123</v>
       </c>
       <c r="C37" t="n">
-        <v>14811423</v>
+        <v>66060365</v>
       </c>
     </row>
     <row r="38">
@@ -1466,10 +1466,10 @@
         <v>36</v>
       </c>
       <c r="B38" t="n">
-        <v>121037906</v>
+        <v>132316197</v>
       </c>
       <c r="C38" t="n">
-        <v>19702613</v>
+        <v>66122916</v>
       </c>
     </row>
     <row r="39">
@@ -1477,10 +1477,10 @@
         <v>37</v>
       </c>
       <c r="B39" t="n">
-        <v>133322687</v>
+        <v>131793861</v>
       </c>
       <c r="C39" t="n">
-        <v>27880481</v>
+        <v>65806805</v>
       </c>
     </row>
     <row r="40">
@@ -1488,10 +1488,10 @@
         <v>38</v>
       </c>
       <c r="B40" t="n">
-        <v>142765202</v>
+        <v>130828834</v>
       </c>
       <c r="C40" t="n">
-        <v>37714500</v>
+        <v>65553332</v>
       </c>
     </row>
     <row r="41">
@@ -1499,10 +1499,10 @@
         <v>39</v>
       </c>
       <c r="B41" t="n">
-        <v>145494497</v>
+        <v>130057197</v>
       </c>
       <c r="C41" t="n">
-        <v>44774072</v>
+        <v>65126814</v>
       </c>
     </row>
     <row r="42">
@@ -1510,10 +1510,10 @@
         <v>40</v>
       </c>
       <c r="B42" t="n">
-        <v>144298983</v>
+        <v>129635018</v>
       </c>
       <c r="C42" t="n">
-        <v>48529483</v>
+        <v>64341412</v>
       </c>
     </row>
     <row r="43">
@@ -1521,10 +1521,10 @@
         <v>41</v>
       </c>
       <c r="B43" t="n">
-        <v>142478114</v>
+        <v>128454351</v>
       </c>
       <c r="C43" t="n">
-        <v>50019456</v>
+        <v>63714766</v>
       </c>
     </row>
     <row r="44">
@@ -1532,10 +1532,10 @@
         <v>42</v>
       </c>
       <c r="B44" t="n">
-        <v>140893185</v>
+        <v>127521405</v>
       </c>
       <c r="C44" t="n">
-        <v>50772450</v>
+        <v>63221221</v>
       </c>
     </row>
     <row r="45">
@@ -1543,10 +1543,10 @@
         <v>43</v>
       </c>
       <c r="B45" t="n">
-        <v>139296757</v>
+        <v>125865151</v>
       </c>
       <c r="C45" t="n">
-        <v>50922959</v>
+        <v>62444763</v>
       </c>
     </row>
     <row r="46">
@@ -1554,10 +1554,10 @@
         <v>44</v>
       </c>
       <c r="B46" t="n">
-        <v>137538135</v>
+        <v>124765478</v>
       </c>
       <c r="C46" t="n">
-        <v>50905221</v>
+        <v>61866385</v>
       </c>
     </row>
     <row r="47">
@@ -1565,10 +1565,10 @@
         <v>45</v>
       </c>
       <c r="B47" t="n">
-        <v>136294900</v>
+        <v>124024020</v>
       </c>
       <c r="C47" t="n">
-        <v>51359391</v>
+        <v>61250103</v>
       </c>
     </row>
     <row r="48">
@@ -1576,10 +1576,10 @@
         <v>46</v>
       </c>
       <c r="B48" t="n">
-        <v>134418411</v>
+        <v>122976577</v>
       </c>
       <c r="C48" t="n">
-        <v>51674901</v>
+        <v>60475519</v>
       </c>
     </row>
     <row r="49">
@@ -1587,10 +1587,10 @@
         <v>47</v>
       </c>
       <c r="B49" t="n">
-        <v>132555244</v>
+        <v>121767955</v>
       </c>
       <c r="C49" t="n">
-        <v>51847987</v>
+        <v>59797490</v>
       </c>
     </row>
     <row r="50">
@@ -1598,10 +1598,10 @@
         <v>48</v>
       </c>
       <c r="B50" t="n">
-        <v>131098964</v>
+        <v>120682782</v>
       </c>
       <c r="C50" t="n">
-        <v>51692848</v>
+        <v>58851751</v>
       </c>
     </row>
     <row r="51">
@@ -1609,10 +1609,10 @@
         <v>49</v>
       </c>
       <c r="B51" t="n">
-        <v>130334834</v>
+        <v>119295664</v>
       </c>
       <c r="C51" t="n">
-        <v>51401563</v>
+        <v>58148881</v>
       </c>
     </row>
     <row r="52">
@@ -1620,10 +1620,10 @@
         <v>50</v>
       </c>
       <c r="B52" t="n">
-        <v>129984462</v>
+        <v>117977284</v>
       </c>
       <c r="C52" t="n">
-        <v>51178579</v>
+        <v>57450254</v>
       </c>
     </row>
     <row r="53">
@@ -1631,10 +1631,10 @@
         <v>51</v>
       </c>
       <c r="B53" t="n">
-        <v>129034134</v>
+        <v>117542855</v>
       </c>
       <c r="C53" t="n">
-        <v>50812324</v>
+        <v>56772933</v>
       </c>
     </row>
     <row r="54">
@@ -1642,10 +1642,10 @@
         <v>52</v>
       </c>
       <c r="B54" t="n">
-        <v>128508792</v>
+        <v>116887565</v>
       </c>
       <c r="C54" t="n">
-        <v>50432011</v>
+        <v>56206220</v>
       </c>
     </row>
     <row r="55">
@@ -1653,10 +1653,10 @@
         <v>53</v>
       </c>
       <c r="B55" t="n">
-        <v>127688240</v>
+        <v>116119041</v>
       </c>
       <c r="C55" t="n">
-        <v>49776725</v>
+        <v>55557998</v>
       </c>
     </row>
   </sheetData>
@@ -1690,10 +1690,10 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3564168</v>
+        <v>10373840</v>
       </c>
       <c r="C2" t="n">
-        <v>1928259</v>
+        <v>2274511</v>
       </c>
     </row>
     <row r="3">
@@ -1701,10 +1701,10 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3658851</v>
+        <v>10395508</v>
       </c>
       <c r="C3" t="n">
-        <v>1914407</v>
+        <v>2216649</v>
       </c>
     </row>
     <row r="4">
@@ -1712,10 +1712,10 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3603579</v>
+        <v>10572326</v>
       </c>
       <c r="C4" t="n">
-        <v>1945054</v>
+        <v>2239696</v>
       </c>
     </row>
     <row r="5">
@@ -1723,10 +1723,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3685174</v>
+        <v>10935868</v>
       </c>
       <c r="C5" t="n">
-        <v>1990243</v>
+        <v>2270660</v>
       </c>
     </row>
     <row r="6">
@@ -1734,10 +1734,10 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>3777077</v>
+        <v>11103151</v>
       </c>
       <c r="C6" t="n">
-        <v>2024487</v>
+        <v>2294136</v>
       </c>
     </row>
     <row r="7">
@@ -1745,10 +1745,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>3585896</v>
+        <v>11430242</v>
       </c>
       <c r="C7" t="n">
-        <v>2085012</v>
+        <v>2294763</v>
       </c>
     </row>
     <row r="8">
@@ -1756,10 +1756,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>3587973</v>
+        <v>11220620</v>
       </c>
       <c r="C8" t="n">
-        <v>2125142</v>
+        <v>2320150</v>
       </c>
     </row>
     <row r="9">
@@ -1767,10 +1767,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>3513831</v>
+        <v>11515084</v>
       </c>
       <c r="C9" t="n">
-        <v>2165487</v>
+        <v>2344030</v>
       </c>
     </row>
     <row r="10">
@@ -1778,10 +1778,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3579693</v>
+        <v>11922435</v>
       </c>
       <c r="C10" t="n">
-        <v>2212353</v>
+        <v>2388373</v>
       </c>
     </row>
     <row r="11">
@@ -1789,10 +1789,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3526937</v>
+        <v>12170494</v>
       </c>
       <c r="C11" t="n">
-        <v>2278026</v>
+        <v>2468663</v>
       </c>
     </row>
     <row r="12">
@@ -1800,10 +1800,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3481168</v>
+        <v>12767624</v>
       </c>
       <c r="C12" t="n">
-        <v>2350741</v>
+        <v>2541373</v>
       </c>
     </row>
     <row r="13">
@@ -1811,10 +1811,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3511665</v>
+        <v>13393573</v>
       </c>
       <c r="C13" t="n">
-        <v>2454418</v>
+        <v>2661930</v>
       </c>
     </row>
     <row r="14">
@@ -1822,10 +1822,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>3522374</v>
+        <v>14062130</v>
       </c>
       <c r="C14" t="n">
-        <v>2558354</v>
+        <v>2783441</v>
       </c>
     </row>
     <row r="15">
@@ -1833,10 +1833,10 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>3629268</v>
+        <v>14524727</v>
       </c>
       <c r="C15" t="n">
-        <v>2641381</v>
+        <v>2858541</v>
       </c>
     </row>
     <row r="16">
@@ -1844,10 +1844,10 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3719091</v>
+        <v>15063134</v>
       </c>
       <c r="C16" t="n">
-        <v>2698379</v>
+        <v>2966527</v>
       </c>
     </row>
     <row r="17">
@@ -1855,10 +1855,10 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>3443350</v>
+        <v>15988408</v>
       </c>
       <c r="C17" t="n">
-        <v>2757749</v>
+        <v>3071123</v>
       </c>
     </row>
     <row r="18">
@@ -1866,10 +1866,10 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>3585088</v>
+        <v>16626200</v>
       </c>
       <c r="C18" t="n">
-        <v>2812450</v>
+        <v>3188875</v>
       </c>
     </row>
     <row r="19">
@@ -1877,10 +1877,10 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>3735417</v>
+        <v>17796778</v>
       </c>
       <c r="C19" t="n">
-        <v>2899755</v>
+        <v>3366479</v>
       </c>
     </row>
     <row r="20">
@@ -1888,10 +1888,10 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>3798097</v>
+        <v>19288700</v>
       </c>
       <c r="C20" t="n">
-        <v>3002636</v>
+        <v>3551526</v>
       </c>
     </row>
     <row r="21">
@@ -1899,10 +1899,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>3677459</v>
+        <v>20984741</v>
       </c>
       <c r="C21" t="n">
-        <v>3158409</v>
+        <v>3801438</v>
       </c>
     </row>
     <row r="22">
@@ -1910,10 +1910,10 @@
         <v>20</v>
       </c>
       <c r="B22" t="n">
-        <v>3865382</v>
+        <v>23009257</v>
       </c>
       <c r="C22" t="n">
-        <v>3409935</v>
+        <v>4034916</v>
       </c>
     </row>
     <row r="23">
@@ -1921,10 +1921,10 @@
         <v>21</v>
       </c>
       <c r="B23" t="n">
-        <v>3787056</v>
+        <v>24529413</v>
       </c>
       <c r="C23" t="n">
-        <v>3632092</v>
+        <v>4231193</v>
       </c>
     </row>
     <row r="24">
@@ -1932,10 +1932,10 @@
         <v>22</v>
       </c>
       <c r="B24" t="n">
-        <v>3891331</v>
+        <v>26088672</v>
       </c>
       <c r="C24" t="n">
-        <v>3867261</v>
+        <v>4465809</v>
       </c>
     </row>
     <row r="25">
@@ -1943,10 +1943,10 @@
         <v>23</v>
       </c>
       <c r="B25" t="n">
-        <v>3835745</v>
+        <v>28175897</v>
       </c>
       <c r="C25" t="n">
-        <v>4104604</v>
+        <v>4572249</v>
       </c>
     </row>
     <row r="26">
@@ -1954,10 +1954,10 @@
         <v>24</v>
       </c>
       <c r="B26" t="n">
-        <v>3988388</v>
+        <v>29703763</v>
       </c>
       <c r="C26" t="n">
-        <v>4311137</v>
+        <v>4769104</v>
       </c>
     </row>
     <row r="27">
@@ -1965,10 +1965,10 @@
         <v>25</v>
       </c>
       <c r="B27" t="n">
-        <v>4102009</v>
+        <v>32617400</v>
       </c>
       <c r="C27" t="n">
-        <v>4616925</v>
+        <v>5076143</v>
       </c>
     </row>
     <row r="28">
@@ -1976,10 +1976,10 @@
         <v>26</v>
       </c>
       <c r="B28" t="n">
-        <v>4261253</v>
+        <v>37606987</v>
       </c>
       <c r="C28" t="n">
-        <v>5077453</v>
+        <v>5551006</v>
       </c>
     </row>
     <row r="29">
@@ -1987,10 +1987,10 @@
         <v>27</v>
       </c>
       <c r="B29" t="n">
-        <v>4404492</v>
+        <v>44687145</v>
       </c>
       <c r="C29" t="n">
-        <v>5686989</v>
+        <v>6212618</v>
       </c>
     </row>
     <row r="30">
@@ -1998,10 +1998,10 @@
         <v>28</v>
       </c>
       <c r="B30" t="n">
-        <v>4565802</v>
+        <v>56301217</v>
       </c>
       <c r="C30" t="n">
-        <v>6464915</v>
+        <v>7069723</v>
       </c>
     </row>
     <row r="31">
@@ -2009,10 +2009,10 @@
         <v>29</v>
       </c>
       <c r="B31" t="n">
-        <v>4731233</v>
+        <v>69647947</v>
       </c>
       <c r="C31" t="n">
-        <v>7447379</v>
+        <v>7912394</v>
       </c>
     </row>
     <row r="32">
@@ -2020,10 +2020,10 @@
         <v>30</v>
       </c>
       <c r="B32" t="n">
-        <v>5164599</v>
+        <v>81454154</v>
       </c>
       <c r="C32" t="n">
-        <v>8181672</v>
+        <v>9007136</v>
       </c>
     </row>
     <row r="33">
@@ -2031,10 +2031,10 @@
         <v>31</v>
       </c>
       <c r="B33" t="n">
-        <v>5372512</v>
+        <v>100713376</v>
       </c>
       <c r="C33" t="n">
-        <v>9262585</v>
+        <v>10663077</v>
       </c>
     </row>
     <row r="34">
@@ -2042,10 +2042,10 @@
         <v>32</v>
       </c>
       <c r="B34" t="n">
-        <v>5766148</v>
+        <v>115593385</v>
       </c>
       <c r="C34" t="n">
-        <v>10543845</v>
+        <v>12807316</v>
       </c>
     </row>
     <row r="35">
@@ -2053,10 +2053,10 @@
         <v>33</v>
       </c>
       <c r="B35" t="n">
-        <v>6293268</v>
+        <v>127513463</v>
       </c>
       <c r="C35" t="n">
-        <v>11723879</v>
+        <v>15765525</v>
       </c>
     </row>
     <row r="36">
@@ -2064,10 +2064,10 @@
         <v>34</v>
       </c>
       <c r="B36" t="n">
-        <v>7079656</v>
+        <v>136994749</v>
       </c>
       <c r="C36" t="n">
-        <v>14359263</v>
+        <v>21535877</v>
       </c>
     </row>
     <row r="37">
@@ -2075,10 +2075,10 @@
         <v>35</v>
       </c>
       <c r="B37" t="n">
-        <v>8208453</v>
+        <v>143462453</v>
       </c>
       <c r="C37" t="n">
-        <v>18466192</v>
+        <v>27802432</v>
       </c>
     </row>
     <row r="38">
@@ -2086,10 +2086,10 @@
         <v>36</v>
       </c>
       <c r="B38" t="n">
-        <v>9185664</v>
+        <v>144909782</v>
       </c>
       <c r="C38" t="n">
-        <v>23639719</v>
+        <v>34170146</v>
       </c>
     </row>
     <row r="39">
@@ -2097,10 +2097,10 @@
         <v>37</v>
       </c>
       <c r="B39" t="n">
-        <v>10298286</v>
+        <v>143655088</v>
       </c>
       <c r="C39" t="n">
-        <v>30709716</v>
+        <v>38382723</v>
       </c>
     </row>
     <row r="40">
@@ -2108,10 +2108,10 @@
         <v>38</v>
       </c>
       <c r="B40" t="n">
-        <v>10799962</v>
+        <v>141779484</v>
       </c>
       <c r="C40" t="n">
-        <v>35654496</v>
+        <v>40711242</v>
       </c>
     </row>
     <row r="41">
@@ -2119,10 +2119,10 @@
         <v>39</v>
       </c>
       <c r="B41" t="n">
-        <v>11093096</v>
+        <v>140375042</v>
       </c>
       <c r="C41" t="n">
-        <v>38739593</v>
+        <v>41801312</v>
       </c>
     </row>
     <row r="42">
@@ -2130,10 +2130,10 @@
         <v>40</v>
       </c>
       <c r="B42" t="n">
-        <v>11068703</v>
+        <v>139660858</v>
       </c>
       <c r="C42" t="n">
-        <v>40660871</v>
+        <v>42360572</v>
       </c>
     </row>
     <row r="43">
@@ -2141,10 +2141,10 @@
         <v>41</v>
       </c>
       <c r="B43" t="n">
-        <v>11307019</v>
+        <v>138478846</v>
       </c>
       <c r="C43" t="n">
-        <v>41631759</v>
+        <v>42563299</v>
       </c>
     </row>
     <row r="44">
@@ -2152,10 +2152,10 @@
         <v>42</v>
       </c>
       <c r="B44" t="n">
-        <v>11297690</v>
+        <v>137950270</v>
       </c>
       <c r="C44" t="n">
-        <v>42375103</v>
+        <v>42767540</v>
       </c>
     </row>
     <row r="45">
@@ -2163,10 +2163,10 @@
         <v>43</v>
       </c>
       <c r="B45" t="n">
-        <v>11290199</v>
+        <v>137385129</v>
       </c>
       <c r="C45" t="n">
-        <v>43115615</v>
+        <v>43030011</v>
       </c>
     </row>
     <row r="46">
@@ -2174,10 +2174,10 @@
         <v>44</v>
       </c>
       <c r="B46" t="n">
-        <v>11294001</v>
+        <v>136876853</v>
       </c>
       <c r="C46" t="n">
-        <v>43604020</v>
+        <v>43418762</v>
       </c>
     </row>
     <row r="47">
@@ -2185,10 +2185,10 @@
         <v>45</v>
       </c>
       <c r="B47" t="n">
-        <v>11545577</v>
+        <v>135843181</v>
       </c>
       <c r="C47" t="n">
-        <v>44155848</v>
+        <v>43685551</v>
       </c>
     </row>
     <row r="48">
@@ -2196,10 +2196,10 @@
         <v>46</v>
       </c>
       <c r="B48" t="n">
-        <v>11463028</v>
+        <v>134980517</v>
       </c>
       <c r="C48" t="n">
-        <v>44172068</v>
+        <v>43659854</v>
       </c>
     </row>
     <row r="49">
@@ -2207,10 +2207,10 @@
         <v>47</v>
       </c>
       <c r="B49" t="n">
-        <v>11589469</v>
+        <v>135049403</v>
       </c>
       <c r="C49" t="n">
-        <v>43995044</v>
+        <v>43516069</v>
       </c>
     </row>
     <row r="50">
@@ -2218,10 +2218,10 @@
         <v>48</v>
       </c>
       <c r="B50" t="n">
-        <v>11587630</v>
+        <v>134013177</v>
       </c>
       <c r="C50" t="n">
-        <v>43743331</v>
+        <v>43298163</v>
       </c>
     </row>
     <row r="51">
@@ -2229,10 +2229,10 @@
         <v>49</v>
       </c>
       <c r="B51" t="n">
-        <v>11579421</v>
+        <v>133867116</v>
       </c>
       <c r="C51" t="n">
-        <v>43653846</v>
+        <v>43090243</v>
       </c>
     </row>
     <row r="52">
@@ -2240,10 +2240,10 @@
         <v>50</v>
       </c>
       <c r="B52" t="n">
-        <v>11712218</v>
+        <v>132499197</v>
       </c>
       <c r="C52" t="n">
-        <v>43366126</v>
+        <v>42899983</v>
       </c>
     </row>
     <row r="53">
@@ -2251,10 +2251,10 @@
         <v>51</v>
       </c>
       <c r="B53" t="n">
-        <v>11711076</v>
+        <v>131760431</v>
       </c>
       <c r="C53" t="n">
-        <v>43410988</v>
+        <v>42678870</v>
       </c>
     </row>
     <row r="54">
@@ -2262,10 +2262,10 @@
         <v>52</v>
       </c>
       <c r="B54" t="n">
-        <v>11855383</v>
+        <v>130545596</v>
       </c>
       <c r="C54" t="n">
-        <v>43272138</v>
+        <v>42215971</v>
       </c>
     </row>
     <row r="55">
@@ -2273,10 +2273,10 @@
         <v>53</v>
       </c>
       <c r="B55" t="n">
-        <v>11670588</v>
+        <v>129556257</v>
       </c>
       <c r="C55" t="n">
-        <v>43057844</v>
+        <v>41715203</v>
       </c>
     </row>
   </sheetData>
@@ -2310,10 +2310,10 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3284328</v>
+        <v>3958179</v>
       </c>
       <c r="C2" t="n">
-        <v>1890379</v>
+        <v>2466407</v>
       </c>
     </row>
     <row r="3">
@@ -2321,10 +2321,10 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3142009</v>
+        <v>4034121</v>
       </c>
       <c r="C3" t="n">
-        <v>1909887</v>
+        <v>2512031</v>
       </c>
     </row>
     <row r="4">
@@ -2332,10 +2332,10 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3298046</v>
+        <v>3946796</v>
       </c>
       <c r="C4" t="n">
-        <v>1939434</v>
+        <v>2559109</v>
       </c>
     </row>
     <row r="5">
@@ -2343,10 +2343,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3387896</v>
+        <v>3877278</v>
       </c>
       <c r="C5" t="n">
-        <v>1980395</v>
+        <v>2599285</v>
       </c>
     </row>
     <row r="6">
@@ -2354,10 +2354,10 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>3277799</v>
+        <v>3918934</v>
       </c>
       <c r="C6" t="n">
-        <v>2005192</v>
+        <v>2637736</v>
       </c>
     </row>
     <row r="7">
@@ -2365,10 +2365,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>3278030</v>
+        <v>4048782</v>
       </c>
       <c r="C7" t="n">
-        <v>2026570</v>
+        <v>2661169</v>
       </c>
     </row>
     <row r="8">
@@ -2376,10 +2376,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>3470845</v>
+        <v>4253843</v>
       </c>
       <c r="C8" t="n">
-        <v>2037392</v>
+        <v>2694972</v>
       </c>
     </row>
     <row r="9">
@@ -2387,10 +2387,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>3415971</v>
+        <v>4033614</v>
       </c>
       <c r="C9" t="n">
-        <v>2053296</v>
+        <v>2750336</v>
       </c>
     </row>
     <row r="10">
@@ -2398,10 +2398,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3347466</v>
+        <v>4060189</v>
       </c>
       <c r="C10" t="n">
-        <v>2071239</v>
+        <v>2826771</v>
       </c>
     </row>
     <row r="11">
@@ -2409,10 +2409,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3311532</v>
+        <v>4039991</v>
       </c>
       <c r="C11" t="n">
-        <v>2117084</v>
+        <v>2925846</v>
       </c>
     </row>
     <row r="12">
@@ -2420,10 +2420,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3365005</v>
+        <v>4037713</v>
       </c>
       <c r="C12" t="n">
-        <v>2165982</v>
+        <v>3051457</v>
       </c>
     </row>
     <row r="13">
@@ -2431,10 +2431,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3421414</v>
+        <v>4115428</v>
       </c>
       <c r="C13" t="n">
-        <v>2234544</v>
+        <v>3149113</v>
       </c>
     </row>
     <row r="14">
@@ -2442,10 +2442,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>3407850</v>
+        <v>4088430</v>
       </c>
       <c r="C14" t="n">
-        <v>2311880</v>
+        <v>3282020</v>
       </c>
     </row>
     <row r="15">
@@ -2453,10 +2453,10 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>3424628</v>
+        <v>4105084</v>
       </c>
       <c r="C15" t="n">
-        <v>2378747</v>
+        <v>3403647</v>
       </c>
     </row>
     <row r="16">
@@ -2464,10 +2464,10 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3454549</v>
+        <v>4143792</v>
       </c>
       <c r="C16" t="n">
-        <v>2432085</v>
+        <v>3493934</v>
       </c>
     </row>
     <row r="17">
@@ -2475,10 +2475,10 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>3468784</v>
+        <v>4118621</v>
       </c>
       <c r="C17" t="n">
-        <v>2497558</v>
+        <v>3621677</v>
       </c>
     </row>
     <row r="18">
@@ -2486,10 +2486,10 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>3244162</v>
+        <v>4284929</v>
       </c>
       <c r="C18" t="n">
-        <v>2569651</v>
+        <v>3808624</v>
       </c>
     </row>
     <row r="19">
@@ -2497,10 +2497,10 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>3318406</v>
+        <v>4405629</v>
       </c>
       <c r="C19" t="n">
-        <v>2649493</v>
+        <v>4073223</v>
       </c>
     </row>
     <row r="20">
@@ -2508,10 +2508,10 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>3230389</v>
+        <v>4371881</v>
       </c>
       <c r="C20" t="n">
-        <v>2788561</v>
+        <v>4321029</v>
       </c>
     </row>
     <row r="21">
@@ -2519,10 +2519,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>3236235</v>
+        <v>4450487</v>
       </c>
       <c r="C21" t="n">
-        <v>2915508</v>
+        <v>4596869</v>
       </c>
     </row>
     <row r="22">
@@ -2530,10 +2530,10 @@
         <v>20</v>
       </c>
       <c r="B22" t="n">
-        <v>3375621</v>
+        <v>4259241</v>
       </c>
       <c r="C22" t="n">
-        <v>3074041</v>
+        <v>4855725</v>
       </c>
     </row>
     <row r="23">
@@ -2541,10 +2541,10 @@
         <v>21</v>
       </c>
       <c r="B23" t="n">
-        <v>3412394</v>
+        <v>4669458</v>
       </c>
       <c r="C23" t="n">
-        <v>3201710</v>
+        <v>5038967</v>
       </c>
     </row>
     <row r="24">
@@ -2552,10 +2552,10 @@
         <v>22</v>
       </c>
       <c r="B24" t="n">
-        <v>3469668</v>
+        <v>4664038</v>
       </c>
       <c r="C24" t="n">
-        <v>3300543</v>
+        <v>5236756</v>
       </c>
     </row>
     <row r="25">
@@ -2563,10 +2563,10 @@
         <v>23</v>
       </c>
       <c r="B25" t="n">
-        <v>3779935</v>
+        <v>4803822</v>
       </c>
       <c r="C25" t="n">
-        <v>3386703</v>
+        <v>5502232</v>
       </c>
     </row>
     <row r="26">
@@ -2574,10 +2574,10 @@
         <v>24</v>
       </c>
       <c r="B26" t="n">
-        <v>3718465</v>
+        <v>4808400</v>
       </c>
       <c r="C26" t="n">
-        <v>3462694</v>
+        <v>5785429</v>
       </c>
     </row>
     <row r="27">
@@ -2585,10 +2585,10 @@
         <v>25</v>
       </c>
       <c r="B27" t="n">
-        <v>3528450</v>
+        <v>4918224</v>
       </c>
       <c r="C27" t="n">
-        <v>3652627</v>
+        <v>6364124</v>
       </c>
     </row>
     <row r="28">
@@ -2596,10 +2596,10 @@
         <v>26</v>
       </c>
       <c r="B28" t="n">
-        <v>3656176</v>
+        <v>5064334</v>
       </c>
       <c r="C28" t="n">
-        <v>3911944</v>
+        <v>7133851</v>
       </c>
     </row>
     <row r="29">
@@ -2607,10 +2607,10 @@
         <v>27</v>
       </c>
       <c r="B29" t="n">
-        <v>3702532</v>
+        <v>5202067</v>
       </c>
       <c r="C29" t="n">
-        <v>4193401</v>
+        <v>8069707</v>
       </c>
     </row>
     <row r="30">
@@ -2618,10 +2618,10 @@
         <v>28</v>
       </c>
       <c r="B30" t="n">
-        <v>3872976</v>
+        <v>5828861</v>
       </c>
       <c r="C30" t="n">
-        <v>4541316</v>
+        <v>9254627</v>
       </c>
     </row>
     <row r="31">
@@ -2629,10 +2629,10 @@
         <v>29</v>
       </c>
       <c r="B31" t="n">
-        <v>4008191</v>
+        <v>6091402</v>
       </c>
       <c r="C31" t="n">
-        <v>4966191</v>
+        <v>10608671</v>
       </c>
     </row>
     <row r="32">
@@ -2640,10 +2640,10 @@
         <v>30</v>
       </c>
       <c r="B32" t="n">
-        <v>4063320</v>
+        <v>6625035</v>
       </c>
       <c r="C32" t="n">
-        <v>5361592</v>
+        <v>12294585</v>
       </c>
     </row>
     <row r="33">
@@ -2651,10 +2651,10 @@
         <v>31</v>
       </c>
       <c r="B33" t="n">
-        <v>4337034</v>
+        <v>7587797</v>
       </c>
       <c r="C33" t="n">
-        <v>5758669</v>
+        <v>14358738</v>
       </c>
     </row>
     <row r="34">
@@ -2662,10 +2662,10 @@
         <v>32</v>
       </c>
       <c r="B34" t="n">
-        <v>4471281</v>
+        <v>8540042</v>
       </c>
       <c r="C34" t="n">
-        <v>6326445</v>
+        <v>17939318</v>
       </c>
     </row>
     <row r="35">
@@ -2673,10 +2673,10 @@
         <v>33</v>
       </c>
       <c r="B35" t="n">
-        <v>4623192</v>
+        <v>9852828</v>
       </c>
       <c r="C35" t="n">
-        <v>7112378</v>
+        <v>23735967</v>
       </c>
     </row>
     <row r="36">
@@ -2684,10 +2684,10 @@
         <v>34</v>
       </c>
       <c r="B36" t="n">
-        <v>5207942</v>
+        <v>10924544</v>
       </c>
       <c r="C36" t="n">
-        <v>8472380</v>
+        <v>32776765</v>
       </c>
     </row>
     <row r="37">
@@ -2695,10 +2695,10 @@
         <v>35</v>
       </c>
       <c r="B37" t="n">
-        <v>5981916</v>
+        <v>11753255</v>
       </c>
       <c r="C37" t="n">
-        <v>10379379</v>
+        <v>41358728</v>
       </c>
     </row>
     <row r="38">
@@ -2706,10 +2706,10 @@
         <v>36</v>
       </c>
       <c r="B38" t="n">
-        <v>7071610</v>
+        <v>12347056</v>
       </c>
       <c r="C38" t="n">
-        <v>13201107</v>
+        <v>47898844</v>
       </c>
     </row>
     <row r="39">
@@ -2717,10 +2717,10 @@
         <v>37</v>
       </c>
       <c r="B39" t="n">
-        <v>8290059</v>
+        <v>12559488</v>
       </c>
       <c r="C39" t="n">
-        <v>17028668</v>
+        <v>51261262</v>
       </c>
     </row>
     <row r="40">
@@ -2728,10 +2728,10 @@
         <v>38</v>
       </c>
       <c r="B40" t="n">
-        <v>8912586</v>
+        <v>12640463</v>
       </c>
       <c r="C40" t="n">
-        <v>20962254</v>
+        <v>53098323</v>
       </c>
     </row>
     <row r="41">
@@ -2739,10 +2739,10 @@
         <v>39</v>
       </c>
       <c r="B41" t="n">
-        <v>9927381</v>
+        <v>12657833</v>
       </c>
       <c r="C41" t="n">
-        <v>24734291</v>
+        <v>54005563</v>
       </c>
     </row>
     <row r="42">
@@ -2750,10 +2750,10 @@
         <v>40</v>
       </c>
       <c r="B42" t="n">
-        <v>10505415</v>
+        <v>12842546</v>
       </c>
       <c r="C42" t="n">
-        <v>29186031</v>
+        <v>54940456</v>
       </c>
     </row>
     <row r="43">
@@ -2761,10 +2761,10 @@
         <v>41</v>
       </c>
       <c r="B43" t="n">
-        <v>11150806</v>
+        <v>12983385</v>
       </c>
       <c r="C43" t="n">
-        <v>34554951</v>
+        <v>55364500</v>
       </c>
     </row>
     <row r="44">
@@ -2772,10 +2772,10 @@
         <v>42</v>
       </c>
       <c r="B44" t="n">
-        <v>11829755</v>
+        <v>13126959</v>
       </c>
       <c r="C44" t="n">
-        <v>39174781</v>
+        <v>55410341</v>
       </c>
     </row>
     <row r="45">
@@ -2783,10 +2783,10 @@
         <v>43</v>
       </c>
       <c r="B45" t="n">
-        <v>11982277</v>
+        <v>13277492</v>
       </c>
       <c r="C45" t="n">
-        <v>43835136</v>
+        <v>55549871</v>
       </c>
     </row>
     <row r="46">
@@ -2794,10 +2794,10 @@
         <v>44</v>
       </c>
       <c r="B46" t="n">
-        <v>12228838</v>
+        <v>13460579</v>
       </c>
       <c r="C46" t="n">
-        <v>46119257</v>
+        <v>55592966</v>
       </c>
     </row>
     <row r="47">
@@ -2805,10 +2805,10 @@
         <v>45</v>
       </c>
       <c r="B47" t="n">
-        <v>12096250</v>
+        <v>13575740</v>
       </c>
       <c r="C47" t="n">
-        <v>46871144</v>
+        <v>55370543</v>
       </c>
     </row>
     <row r="48">
@@ -2816,10 +2816,10 @@
         <v>46</v>
       </c>
       <c r="B48" t="n">
-        <v>12200012</v>
+        <v>13433338</v>
       </c>
       <c r="C48" t="n">
-        <v>46978876</v>
+        <v>54912687</v>
       </c>
     </row>
     <row r="49">
@@ -2827,10 +2827,10 @@
         <v>47</v>
       </c>
       <c r="B49" t="n">
-        <v>12198773</v>
+        <v>13797728</v>
       </c>
       <c r="C49" t="n">
-        <v>47161248</v>
+        <v>54410714</v>
       </c>
     </row>
     <row r="50">
@@ -2838,10 +2838,10 @@
         <v>48</v>
       </c>
       <c r="B50" t="n">
-        <v>12415535</v>
+        <v>13586231</v>
       </c>
       <c r="C50" t="n">
-        <v>47180105</v>
+        <v>53780131</v>
       </c>
     </row>
     <row r="51">
@@ -2849,10 +2849,10 @@
         <v>49</v>
       </c>
       <c r="B51" t="n">
-        <v>12412493</v>
+        <v>13572560</v>
       </c>
       <c r="C51" t="n">
-        <v>47288403</v>
+        <v>52948404</v>
       </c>
     </row>
     <row r="52">
@@ -2860,10 +2860,10 @@
         <v>50</v>
       </c>
       <c r="B52" t="n">
-        <v>12258922</v>
+        <v>13473972</v>
       </c>
       <c r="C52" t="n">
-        <v>47172548</v>
+        <v>52388311</v>
       </c>
     </row>
     <row r="53">
@@ -2871,10 +2871,10 @@
         <v>51</v>
       </c>
       <c r="B53" t="n">
-        <v>12379497</v>
+        <v>13586310</v>
       </c>
       <c r="C53" t="n">
-        <v>47117150</v>
+        <v>51617446</v>
       </c>
     </row>
     <row r="54">
@@ -2882,10 +2882,10 @@
         <v>52</v>
       </c>
       <c r="B54" t="n">
-        <v>12476832</v>
+        <v>13316110</v>
       </c>
       <c r="C54" t="n">
-        <v>46938583</v>
+        <v>51049885</v>
       </c>
     </row>
     <row r="55">
@@ -2893,10 +2893,10 @@
         <v>53</v>
       </c>
       <c r="B55" t="n">
-        <v>12372701</v>
+        <v>13370588</v>
       </c>
       <c r="C55" t="n">
-        <v>46609455</v>
+        <v>50534738</v>
       </c>
     </row>
   </sheetData>
@@ -2930,10 +2930,10 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2959600</v>
+        <v>4040824</v>
       </c>
       <c r="C2" t="n">
-        <v>2029578</v>
+        <v>2614067</v>
       </c>
     </row>
     <row r="3">
@@ -2941,10 +2941,10 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2807172</v>
+        <v>4195635</v>
       </c>
       <c r="C3" t="n">
-        <v>2017813</v>
+        <v>2577611</v>
       </c>
     </row>
     <row r="4">
@@ -2952,10 +2952,10 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2986687</v>
+        <v>4082364</v>
       </c>
       <c r="C4" t="n">
-        <v>2038468</v>
+        <v>2579606</v>
       </c>
     </row>
     <row r="5">
@@ -2963,10 +2963,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3032509</v>
+        <v>4120155</v>
       </c>
       <c r="C5" t="n">
-        <v>2071968</v>
+        <v>2599444</v>
       </c>
     </row>
     <row r="6">
@@ -2974,10 +2974,10 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>3078462</v>
+        <v>4042867</v>
       </c>
       <c r="C6" t="n">
-        <v>2128539</v>
+        <v>2655615</v>
       </c>
     </row>
     <row r="7">
@@ -2985,10 +2985,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>2988311</v>
+        <v>4107322</v>
       </c>
       <c r="C7" t="n">
-        <v>2186389</v>
+        <v>2739346</v>
       </c>
     </row>
     <row r="8">
@@ -2996,10 +2996,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>3292352</v>
+        <v>4313992</v>
       </c>
       <c r="C8" t="n">
-        <v>2265376</v>
+        <v>2797752</v>
       </c>
     </row>
     <row r="9">
@@ -3007,10 +3007,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>3086476</v>
+        <v>4235956</v>
       </c>
       <c r="C9" t="n">
-        <v>2343057</v>
+        <v>2856770</v>
       </c>
     </row>
     <row r="10">
@@ -3018,10 +3018,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3113386</v>
+        <v>4127669</v>
       </c>
       <c r="C10" t="n">
-        <v>2442515</v>
+        <v>2916751</v>
       </c>
     </row>
     <row r="11">
@@ -3029,10 +3029,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3244828</v>
+        <v>3822554</v>
       </c>
       <c r="C11" t="n">
-        <v>2495237</v>
+        <v>3037336</v>
       </c>
     </row>
     <row r="12">
@@ -3040,10 +3040,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3037727</v>
+        <v>4166025</v>
       </c>
       <c r="C12" t="n">
-        <v>2568327</v>
+        <v>3111523</v>
       </c>
     </row>
     <row r="13">
@@ -3051,10 +3051,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3047605</v>
+        <v>4092071</v>
       </c>
       <c r="C13" t="n">
-        <v>2649039</v>
+        <v>3210124</v>
       </c>
     </row>
     <row r="14">
@@ -3062,10 +3062,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>3130858</v>
+        <v>4065198</v>
       </c>
       <c r="C14" t="n">
-        <v>2763272</v>
+        <v>3338460</v>
       </c>
     </row>
     <row r="15">
@@ -3073,10 +3073,10 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>3168863</v>
+        <v>4164473</v>
       </c>
       <c r="C15" t="n">
-        <v>2914162</v>
+        <v>3472953</v>
       </c>
     </row>
     <row r="16">
@@ -3084,10 +3084,10 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3185053</v>
+        <v>4384909</v>
       </c>
       <c r="C16" t="n">
-        <v>3078034</v>
+        <v>3648473</v>
       </c>
     </row>
     <row r="17">
@@ -3095,10 +3095,10 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>3145319</v>
+        <v>4102103</v>
       </c>
       <c r="C17" t="n">
-        <v>3252434</v>
+        <v>3750894</v>
       </c>
     </row>
     <row r="18">
@@ -3106,10 +3106,10 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>3311950</v>
+        <v>4064112</v>
       </c>
       <c r="C18" t="n">
-        <v>3390003</v>
+        <v>3871050</v>
       </c>
     </row>
     <row r="19">
@@ -3117,10 +3117,10 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>3271675</v>
+        <v>4109594</v>
       </c>
       <c r="C19" t="n">
-        <v>3497791</v>
+        <v>3997087</v>
       </c>
     </row>
     <row r="20">
@@ -3128,10 +3128,10 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>3324997</v>
+        <v>4186272</v>
       </c>
       <c r="C20" t="n">
-        <v>3626485</v>
+        <v>4086329</v>
       </c>
     </row>
     <row r="21">
@@ -3139,10 +3139,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>3369821</v>
+        <v>4083482</v>
       </c>
       <c r="C21" t="n">
-        <v>3764129</v>
+        <v>4286140</v>
       </c>
     </row>
     <row r="22">
@@ -3150,10 +3150,10 @@
         <v>20</v>
       </c>
       <c r="B22" t="n">
-        <v>3496468</v>
+        <v>4238931</v>
       </c>
       <c r="C22" t="n">
-        <v>3986530</v>
+        <v>4478944</v>
       </c>
     </row>
     <row r="23">
@@ -3161,10 +3161,10 @@
         <v>21</v>
       </c>
       <c r="B23" t="n">
-        <v>3380890</v>
+        <v>4161332</v>
       </c>
       <c r="C23" t="n">
-        <v>4257545</v>
+        <v>4721289</v>
       </c>
     </row>
     <row r="24">
@@ -3172,10 +3172,10 @@
         <v>22</v>
       </c>
       <c r="B24" t="n">
-        <v>3439150</v>
+        <v>4262784</v>
       </c>
       <c r="C24" t="n">
-        <v>4621209</v>
+        <v>5066693</v>
       </c>
     </row>
     <row r="25">
@@ -3183,10 +3183,10 @@
         <v>23</v>
       </c>
       <c r="B25" t="n">
-        <v>3458030</v>
+        <v>4337049</v>
       </c>
       <c r="C25" t="n">
-        <v>5106604</v>
+        <v>5443220</v>
       </c>
     </row>
     <row r="26">
@@ -3194,10 +3194,10 @@
         <v>24</v>
       </c>
       <c r="B26" t="n">
-        <v>3672712</v>
+        <v>4509581</v>
       </c>
       <c r="C26" t="n">
-        <v>5497278</v>
+        <v>5875575</v>
       </c>
     </row>
     <row r="27">
@@ -3205,10 +3205,10 @@
         <v>25</v>
       </c>
       <c r="B27" t="n">
-        <v>3812339</v>
+        <v>4620046</v>
       </c>
       <c r="C27" t="n">
-        <v>6049993</v>
+        <v>6249327</v>
       </c>
     </row>
     <row r="28">
@@ -3216,10 +3216,10 @@
         <v>26</v>
       </c>
       <c r="B28" t="n">
-        <v>4063753</v>
+        <v>4816180</v>
       </c>
       <c r="C28" t="n">
-        <v>6661557</v>
+        <v>6717929</v>
       </c>
     </row>
     <row r="29">
@@ -3227,10 +3227,10 @@
         <v>27</v>
       </c>
       <c r="B29" t="n">
-        <v>4219170</v>
+        <v>4724307</v>
       </c>
       <c r="C29" t="n">
-        <v>7482963</v>
+        <v>7235753</v>
       </c>
     </row>
     <row r="30">
@@ -3238,10 +3238,10 @@
         <v>28</v>
       </c>
       <c r="B30" t="n">
-        <v>4494719</v>
+        <v>5053979</v>
       </c>
       <c r="C30" t="n">
-        <v>8721925</v>
+        <v>7987565</v>
       </c>
     </row>
     <row r="31">
@@ -3249,10 +3249,10 @@
         <v>29</v>
       </c>
       <c r="B31" t="n">
-        <v>5150062</v>
+        <v>5274874</v>
       </c>
       <c r="C31" t="n">
-        <v>10618136</v>
+        <v>9196256</v>
       </c>
     </row>
     <row r="32">
@@ -3260,10 +3260,10 @@
         <v>30</v>
       </c>
       <c r="B32" t="n">
-        <v>6179232</v>
+        <v>6020342</v>
       </c>
       <c r="C32" t="n">
-        <v>13864320</v>
+        <v>10825407</v>
       </c>
     </row>
     <row r="33">
@@ -3271,10 +3271,10 @@
         <v>31</v>
       </c>
       <c r="B33" t="n">
-        <v>7202233</v>
+        <v>6770032</v>
       </c>
       <c r="C33" t="n">
-        <v>19167627</v>
+        <v>13006790</v>
       </c>
     </row>
     <row r="34">
@@ -3282,10 +3282,10 @@
         <v>32</v>
       </c>
       <c r="B34" t="n">
-        <v>8092332</v>
+        <v>7692123</v>
       </c>
       <c r="C34" t="n">
-        <v>24380796</v>
+        <v>15871000</v>
       </c>
     </row>
     <row r="35">
@@ -3293,10 +3293,10 @@
         <v>33</v>
       </c>
       <c r="B35" t="n">
-        <v>8798873</v>
+        <v>8500249</v>
       </c>
       <c r="C35" t="n">
-        <v>30361908</v>
+        <v>18813979</v>
       </c>
     </row>
     <row r="36">
@@ -3304,10 +3304,10 @@
         <v>34</v>
       </c>
       <c r="B36" t="n">
-        <v>9380141</v>
+        <v>8914185</v>
       </c>
       <c r="C36" t="n">
-        <v>34738181</v>
+        <v>21798344</v>
       </c>
     </row>
     <row r="37">
@@ -3315,10 +3315,10 @@
         <v>35</v>
       </c>
       <c r="B37" t="n">
-        <v>9533537</v>
+        <v>9751480</v>
       </c>
       <c r="C37" t="n">
-        <v>39021021</v>
+        <v>25211763</v>
       </c>
     </row>
     <row r="38">
@@ -3326,10 +3326,10 @@
         <v>36</v>
       </c>
       <c r="B38" t="n">
-        <v>10056115</v>
+        <v>10489917</v>
       </c>
       <c r="C38" t="n">
-        <v>42592730</v>
+        <v>30574912</v>
       </c>
     </row>
     <row r="39">
@@ -3337,10 +3337,10 @@
         <v>37</v>
       </c>
       <c r="B39" t="n">
-        <v>10265516</v>
+        <v>11408538</v>
       </c>
       <c r="C39" t="n">
-        <v>45104430</v>
+        <v>37885170</v>
       </c>
     </row>
     <row r="40">
@@ -3348,10 +3348,10 @@
         <v>38</v>
       </c>
       <c r="B40" t="n">
-        <v>10385672</v>
+        <v>11926183</v>
       </c>
       <c r="C40" t="n">
-        <v>47224037</v>
+        <v>46016291</v>
       </c>
     </row>
     <row r="41">
@@ -3359,10 +3359,10 @@
         <v>39</v>
       </c>
       <c r="B41" t="n">
-        <v>10394369</v>
+        <v>12313826</v>
       </c>
       <c r="C41" t="n">
-        <v>48039749</v>
+        <v>52897932</v>
       </c>
     </row>
     <row r="42">
@@ -3370,10 +3370,10 @@
         <v>40</v>
       </c>
       <c r="B42" t="n">
-        <v>10719091</v>
+        <v>12569043</v>
       </c>
       <c r="C42" t="n">
-        <v>48369397</v>
+        <v>56559784</v>
       </c>
     </row>
     <row r="43">
@@ -3381,10 +3381,10 @@
         <v>41</v>
       </c>
       <c r="B43" t="n">
-        <v>10530933</v>
+        <v>12481234</v>
       </c>
       <c r="C43" t="n">
-        <v>48591789</v>
+        <v>58072445</v>
       </c>
     </row>
     <row r="44">
@@ -3392,10 +3392,10 @@
         <v>42</v>
       </c>
       <c r="B44" t="n">
-        <v>10818384</v>
+        <v>12688132</v>
       </c>
       <c r="C44" t="n">
-        <v>48938079</v>
+        <v>58741440</v>
       </c>
     </row>
     <row r="45">
@@ -3403,10 +3403,10 @@
         <v>43</v>
       </c>
       <c r="B45" t="n">
-        <v>10788940</v>
+        <v>12609366</v>
       </c>
       <c r="C45" t="n">
-        <v>48921324</v>
+        <v>58908681</v>
       </c>
     </row>
     <row r="46">
@@ -3414,10 +3414,10 @@
         <v>44</v>
       </c>
       <c r="B46" t="n">
-        <v>10860040</v>
+        <v>12730105</v>
       </c>
       <c r="C46" t="n">
-        <v>48614664</v>
+        <v>58752802</v>
       </c>
     </row>
     <row r="47">
@@ -3425,10 +3425,10 @@
         <v>45</v>
       </c>
       <c r="B47" t="n">
-        <v>10739950</v>
+        <v>12723357</v>
       </c>
       <c r="C47" t="n">
-        <v>48230876</v>
+        <v>58973449</v>
       </c>
     </row>
     <row r="48">
@@ -3436,10 +3436,10 @@
         <v>46</v>
       </c>
       <c r="B48" t="n">
-        <v>10943713</v>
+        <v>12762947</v>
       </c>
       <c r="C48" t="n">
-        <v>47772453</v>
+        <v>58653733</v>
       </c>
     </row>
     <row r="49">
@@ -3447,10 +3447,10 @@
         <v>47</v>
       </c>
       <c r="B49" t="n">
-        <v>10986663</v>
+        <v>12741537</v>
       </c>
       <c r="C49" t="n">
-        <v>47431131</v>
+        <v>58124835</v>
       </c>
     </row>
     <row r="50">
@@ -3458,10 +3458,10 @@
         <v>48</v>
       </c>
       <c r="B50" t="n">
-        <v>10909712</v>
+        <v>12814462</v>
       </c>
       <c r="C50" t="n">
-        <v>47161028</v>
+        <v>57311808</v>
       </c>
     </row>
     <row r="51">
@@ -3469,10 +3469,10 @@
         <v>49</v>
       </c>
       <c r="B51" t="n">
-        <v>10760274</v>
+        <v>12856137</v>
       </c>
       <c r="C51" t="n">
-        <v>46920703</v>
+        <v>56836081</v>
       </c>
     </row>
     <row r="52">
@@ -3480,10 +3480,10 @@
         <v>50</v>
       </c>
       <c r="B52" t="n">
-        <v>10929224</v>
+        <v>12927690</v>
       </c>
       <c r="C52" t="n">
-        <v>46391230</v>
+        <v>56339047</v>
       </c>
     </row>
     <row r="53">
@@ -3491,10 +3491,10 @@
         <v>51</v>
       </c>
       <c r="B53" t="n">
-        <v>11084222</v>
+        <v>12975252</v>
       </c>
       <c r="C53" t="n">
-        <v>46292194</v>
+        <v>56028959</v>
       </c>
     </row>
     <row r="54">
@@ -3502,10 +3502,10 @@
         <v>52</v>
       </c>
       <c r="B54" t="n">
-        <v>11027189</v>
+        <v>13049145</v>
       </c>
       <c r="C54" t="n">
-        <v>45935349</v>
+        <v>55459736</v>
       </c>
     </row>
     <row r="55">
@@ -3513,10 +3513,10 @@
         <v>53</v>
       </c>
       <c r="B55" t="n">
-        <v>11116364</v>
+        <v>13262492</v>
       </c>
       <c r="C55" t="n">
-        <v>45576786</v>
+        <v>55085251</v>
       </c>
     </row>
   </sheetData>
@@ -3550,10 +3550,10 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5049259</v>
+        <v>4016934</v>
       </c>
       <c r="C2" t="n">
-        <v>1200396</v>
+        <v>2294525</v>
       </c>
     </row>
     <row r="3">
@@ -3561,10 +3561,10 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5130067</v>
+        <v>3943610</v>
       </c>
       <c r="C3" t="n">
-        <v>1211448</v>
+        <v>2304308</v>
       </c>
     </row>
     <row r="4">
@@ -3572,10 +3572,10 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>5261919</v>
+        <v>4023356</v>
       </c>
       <c r="C4" t="n">
-        <v>1231869</v>
+        <v>2316019</v>
       </c>
     </row>
     <row r="5">
@@ -3583,10 +3583,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>5365226</v>
+        <v>3917560</v>
       </c>
       <c r="C5" t="n">
-        <v>1285037</v>
+        <v>2315061</v>
       </c>
     </row>
     <row r="6">
@@ -3594,10 +3594,10 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>5731701</v>
+        <v>4111573</v>
       </c>
       <c r="C6" t="n">
-        <v>1321501</v>
+        <v>2316155</v>
       </c>
     </row>
     <row r="7">
@@ -3605,10 +3605,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5961953</v>
+        <v>3994374</v>
       </c>
       <c r="C7" t="n">
-        <v>1377732</v>
+        <v>2308908</v>
       </c>
     </row>
     <row r="8">
@@ -3616,10 +3616,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>6190144</v>
+        <v>3987253</v>
       </c>
       <c r="C8" t="n">
-        <v>1412862</v>
+        <v>2313769</v>
       </c>
     </row>
     <row r="9">
@@ -3627,10 +3627,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6424763</v>
+        <v>4041371</v>
       </c>
       <c r="C9" t="n">
-        <v>1464479</v>
+        <v>2331220</v>
       </c>
     </row>
     <row r="10">
@@ -3638,10 +3638,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6725988</v>
+        <v>4077037</v>
       </c>
       <c r="C10" t="n">
-        <v>1505056</v>
+        <v>2364649</v>
       </c>
     </row>
     <row r="11">
@@ -3649,10 +3649,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>6954383</v>
+        <v>4032530</v>
       </c>
       <c r="C11" t="n">
-        <v>1554444</v>
+        <v>2416252</v>
       </c>
     </row>
     <row r="12">
@@ -3660,10 +3660,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>7342911</v>
+        <v>4127315</v>
       </c>
       <c r="C12" t="n">
-        <v>1625632</v>
+        <v>2486490</v>
       </c>
     </row>
     <row r="13">
@@ -3671,10 +3671,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>7704365</v>
+        <v>4005562</v>
       </c>
       <c r="C13" t="n">
-        <v>1691387</v>
+        <v>2551682</v>
       </c>
     </row>
     <row r="14">
@@ -3682,10 +3682,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>8251333</v>
+        <v>4147609</v>
       </c>
       <c r="C14" t="n">
-        <v>1796686</v>
+        <v>2587335</v>
       </c>
     </row>
     <row r="15">
@@ -3693,10 +3693,10 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>8697997</v>
+        <v>4028509</v>
       </c>
       <c r="C15" t="n">
-        <v>1883520</v>
+        <v>2629121</v>
       </c>
     </row>
     <row r="16">
@@ -3704,10 +3704,10 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>9213641</v>
+        <v>4004332</v>
       </c>
       <c r="C16" t="n">
-        <v>1947535</v>
+        <v>2684849</v>
       </c>
     </row>
     <row r="17">
@@ -3715,10 +3715,10 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>9659602</v>
+        <v>4006632</v>
       </c>
       <c r="C17" t="n">
-        <v>2028931</v>
+        <v>2756700</v>
       </c>
     </row>
     <row r="18">
@@ -3726,10 +3726,10 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>10008613</v>
+        <v>4050729</v>
       </c>
       <c r="C18" t="n">
-        <v>2081199</v>
+        <v>2840582</v>
       </c>
     </row>
     <row r="19">
@@ -3737,10 +3737,10 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>10517594</v>
+        <v>4153347</v>
       </c>
       <c r="C19" t="n">
-        <v>2172843</v>
+        <v>2973547</v>
       </c>
     </row>
     <row r="20">
@@ -3748,10 +3748,10 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>11300000</v>
+        <v>4172389</v>
       </c>
       <c r="C20" t="n">
-        <v>2266429</v>
+        <v>3084927</v>
       </c>
     </row>
     <row r="21">
@@ -3759,10 +3759,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>12201125</v>
+        <v>3961870</v>
       </c>
       <c r="C21" t="n">
-        <v>2423908</v>
+        <v>3220427</v>
       </c>
     </row>
     <row r="22">
@@ -3770,10 +3770,10 @@
         <v>20</v>
       </c>
       <c r="B22" t="n">
-        <v>13550208</v>
+        <v>4174148</v>
       </c>
       <c r="C22" t="n">
-        <v>2588050</v>
+        <v>3287790</v>
       </c>
     </row>
     <row r="23">
@@ -3781,10 +3781,10 @@
         <v>21</v>
       </c>
       <c r="B23" t="n">
-        <v>14802355</v>
+        <v>4164347</v>
       </c>
       <c r="C23" t="n">
-        <v>2801126</v>
+        <v>3361278</v>
       </c>
     </row>
     <row r="24">
@@ -3792,10 +3792,10 @@
         <v>22</v>
       </c>
       <c r="B24" t="n">
-        <v>16444440</v>
+        <v>4052910</v>
       </c>
       <c r="C24" t="n">
-        <v>3022089</v>
+        <v>3417770</v>
       </c>
     </row>
     <row r="25">
@@ -3803,10 +3803,10 @@
         <v>23</v>
       </c>
       <c r="B25" t="n">
-        <v>18075475</v>
+        <v>4192320</v>
       </c>
       <c r="C25" t="n">
-        <v>3246422</v>
+        <v>3504371</v>
       </c>
     </row>
     <row r="26">
@@ -3814,10 +3814,10 @@
         <v>24</v>
       </c>
       <c r="B26" t="n">
-        <v>20035057</v>
+        <v>4147805</v>
       </c>
       <c r="C26" t="n">
-        <v>3491244</v>
+        <v>3651376</v>
       </c>
     </row>
     <row r="27">
@@ -3825,10 +3825,10 @@
         <v>25</v>
       </c>
       <c r="B27" t="n">
-        <v>22407180</v>
+        <v>4284537</v>
       </c>
       <c r="C27" t="n">
-        <v>3768194</v>
+        <v>3857739</v>
       </c>
     </row>
     <row r="28">
@@ -3836,10 +3836,10 @@
         <v>26</v>
       </c>
       <c r="B28" t="n">
-        <v>26118371</v>
+        <v>4185589</v>
       </c>
       <c r="C28" t="n">
-        <v>4176299</v>
+        <v>4073509</v>
       </c>
     </row>
     <row r="29">
@@ -3847,10 +3847,10 @@
         <v>27</v>
       </c>
       <c r="B29" t="n">
-        <v>31064666</v>
+        <v>4342631</v>
       </c>
       <c r="C29" t="n">
-        <v>4741786</v>
+        <v>4341889</v>
       </c>
     </row>
     <row r="30">
@@ -3858,10 +3858,10 @@
         <v>28</v>
       </c>
       <c r="B30" t="n">
-        <v>39960497</v>
+        <v>4419646</v>
       </c>
       <c r="C30" t="n">
-        <v>5554980</v>
+        <v>4630034</v>
       </c>
     </row>
     <row r="31">
@@ -3869,10 +3869,10 @@
         <v>29</v>
       </c>
       <c r="B31" t="n">
-        <v>52793500</v>
+        <v>4561502</v>
       </c>
       <c r="C31" t="n">
-        <v>6766366</v>
+        <v>4934414</v>
       </c>
     </row>
     <row r="32">
@@ -3880,10 +3880,10 @@
         <v>30</v>
       </c>
       <c r="B32" t="n">
-        <v>66725520</v>
+        <v>4469458</v>
       </c>
       <c r="C32" t="n">
-        <v>8122010</v>
+        <v>5204048</v>
       </c>
     </row>
     <row r="33">
@@ -3891,10 +3891,10 @@
         <v>31</v>
       </c>
       <c r="B33" t="n">
-        <v>78860771</v>
+        <v>4453518</v>
       </c>
       <c r="C33" t="n">
-        <v>9836565</v>
+        <v>5623864</v>
       </c>
     </row>
     <row r="34">
@@ -3902,10 +3902,10 @@
         <v>32</v>
       </c>
       <c r="B34" t="n">
-        <v>90819071</v>
+        <v>4510096</v>
       </c>
       <c r="C34" t="n">
-        <v>11892764</v>
+        <v>6136015</v>
       </c>
     </row>
     <row r="35">
@@ -3913,10 +3913,10 @@
         <v>33</v>
       </c>
       <c r="B35" t="n">
-        <v>99763048</v>
+        <v>4588351</v>
       </c>
       <c r="C35" t="n">
-        <v>14117181</v>
+        <v>6960228</v>
       </c>
     </row>
     <row r="36">
@@ -3924,10 +3924,10 @@
         <v>34</v>
       </c>
       <c r="B36" t="n">
-        <v>108933606</v>
+        <v>4883213</v>
       </c>
       <c r="C36" t="n">
-        <v>17462090</v>
+        <v>8009254</v>
       </c>
     </row>
     <row r="37">
@@ -3935,10 +3935,10 @@
         <v>35</v>
       </c>
       <c r="B37" t="n">
-        <v>117444107</v>
+        <v>5416006</v>
       </c>
       <c r="C37" t="n">
-        <v>21960178</v>
+        <v>9236114</v>
       </c>
     </row>
     <row r="38">
@@ -3946,10 +3946,10 @@
         <v>36</v>
       </c>
       <c r="B38" t="n">
-        <v>125655052</v>
+        <v>5856694</v>
       </c>
       <c r="C38" t="n">
-        <v>27381070</v>
+        <v>10638579</v>
       </c>
     </row>
     <row r="39">
@@ -3957,10 +3957,10 @@
         <v>37</v>
       </c>
       <c r="B39" t="n">
-        <v>131259971</v>
+        <v>6455359</v>
       </c>
       <c r="C39" t="n">
-        <v>31904713</v>
+        <v>12079976</v>
       </c>
     </row>
     <row r="40">
@@ -3968,10 +3968,10 @@
         <v>38</v>
       </c>
       <c r="B40" t="n">
-        <v>133306209</v>
+        <v>6940712</v>
       </c>
       <c r="C40" t="n">
-        <v>34473274</v>
+        <v>13809369</v>
       </c>
     </row>
     <row r="41">
@@ -3979,10 +3979,10 @@
         <v>39</v>
       </c>
       <c r="B41" t="n">
-        <v>133578458</v>
+        <v>7456660</v>
       </c>
       <c r="C41" t="n">
-        <v>35175422</v>
+        <v>15877203</v>
       </c>
     </row>
     <row r="42">
@@ -3990,10 +3990,10 @@
         <v>40</v>
       </c>
       <c r="B42" t="n">
-        <v>133338762</v>
+        <v>8211459</v>
       </c>
       <c r="C42" t="n">
-        <v>35355292</v>
+        <v>18942066</v>
       </c>
     </row>
     <row r="43">
@@ -4001,10 +4001,10 @@
         <v>41</v>
       </c>
       <c r="B43" t="n">
-        <v>133409466</v>
+        <v>8829639</v>
       </c>
       <c r="C43" t="n">
-        <v>35569382</v>
+        <v>23788448</v>
       </c>
     </row>
     <row r="44">
@@ -4012,10 +4012,10 @@
         <v>42</v>
       </c>
       <c r="B44" t="n">
-        <v>133174851</v>
+        <v>9880613</v>
       </c>
       <c r="C44" t="n">
-        <v>35610855</v>
+        <v>30600651</v>
       </c>
     </row>
     <row r="45">
@@ -4023,10 +4023,10 @@
         <v>43</v>
       </c>
       <c r="B45" t="n">
-        <v>133030057</v>
+        <v>10793815</v>
       </c>
       <c r="C45" t="n">
-        <v>35843675</v>
+        <v>37983823</v>
       </c>
     </row>
     <row r="46">
@@ -4034,10 +4034,10 @@
         <v>44</v>
       </c>
       <c r="B46" t="n">
-        <v>132372998</v>
+        <v>11223464</v>
       </c>
       <c r="C46" t="n">
-        <v>35693270</v>
+        <v>43764799</v>
       </c>
     </row>
     <row r="47">
@@ -4045,10 +4045,10 @@
         <v>45</v>
       </c>
       <c r="B47" t="n">
-        <v>131780265</v>
+        <v>11705088</v>
       </c>
       <c r="C47" t="n">
-        <v>35217116</v>
+        <v>48392853</v>
       </c>
     </row>
     <row r="48">
@@ -4056,10 +4056,10 @@
         <v>46</v>
       </c>
       <c r="B48" t="n">
-        <v>131490457</v>
+        <v>11660400</v>
       </c>
       <c r="C48" t="n">
-        <v>34884076</v>
+        <v>50568329</v>
       </c>
     </row>
     <row r="49">
@@ -4067,10 +4067,10 @@
         <v>47</v>
       </c>
       <c r="B49" t="n">
-        <v>131158922</v>
+        <v>11837484</v>
       </c>
       <c r="C49" t="n">
-        <v>34590293</v>
+        <v>51680001</v>
       </c>
     </row>
     <row r="50">
@@ -4078,10 +4078,10 @@
         <v>48</v>
       </c>
       <c r="B50" t="n">
-        <v>130757777</v>
+        <v>12067713</v>
       </c>
       <c r="C50" t="n">
-        <v>34379342</v>
+        <v>52349092</v>
       </c>
     </row>
     <row r="51">
@@ -4089,10 +4089,10 @@
         <v>49</v>
       </c>
       <c r="B51" t="n">
-        <v>129917111</v>
+        <v>12153546</v>
       </c>
       <c r="C51" t="n">
-        <v>34199544</v>
+        <v>52760167</v>
       </c>
     </row>
     <row r="52">
@@ -4100,10 +4100,10 @@
         <v>50</v>
       </c>
       <c r="B52" t="n">
-        <v>129017763</v>
+        <v>12276840</v>
       </c>
       <c r="C52" t="n">
-        <v>33970389</v>
+        <v>53132790</v>
       </c>
     </row>
     <row r="53">
@@ -4111,10 +4111,10 @@
         <v>51</v>
       </c>
       <c r="B53" t="n">
-        <v>128157586</v>
+        <v>12045225</v>
       </c>
       <c r="C53" t="n">
-        <v>33786096</v>
+        <v>53458187</v>
       </c>
     </row>
     <row r="54">
@@ -4122,10 +4122,10 @@
         <v>52</v>
       </c>
       <c r="B54" t="n">
-        <v>127074654</v>
+        <v>12296807</v>
       </c>
       <c r="C54" t="n">
-        <v>33451451</v>
+        <v>53478598</v>
       </c>
     </row>
     <row r="55">
@@ -4133,10 +4133,10 @@
         <v>53</v>
       </c>
       <c r="B55" t="n">
-        <v>126227812</v>
+        <v>12231877</v>
       </c>
       <c r="C55" t="n">
-        <v>32867373</v>
+        <v>53367575</v>
       </c>
     </row>
   </sheetData>
